--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/83.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/83.xlsx
@@ -426,13 +426,13 @@
         <v>-6.404595613908207</v>
       </c>
       <c r="E2">
-        <v>-4.774666573804958</v>
+        <v>-3.124386490507704</v>
       </c>
       <c r="F2">
-        <v>-5.183120665953501</v>
+        <v>-4.41998222592004</v>
       </c>
       <c r="G2">
-        <v>-6.285750518810233</v>
+        <v>-5.86127568031042</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.788083718292217</v>
       </c>
       <c r="E3">
-        <v>-6.002698155205006</v>
+        <v>-4.129005806739334</v>
       </c>
       <c r="F3">
-        <v>-5.107858517204749</v>
+        <v>-4.784424121516488</v>
       </c>
       <c r="G3">
-        <v>-5.349319675935368</v>
+        <v>-5.640389460839168</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.323940665250281</v>
       </c>
       <c r="E4">
-        <v>-5.887031872101089</v>
+        <v>-4.731446817875753</v>
       </c>
       <c r="F4">
-        <v>-5.420315388071112</v>
+        <v>-4.732171534115298</v>
       </c>
       <c r="G4">
-        <v>-6.172132595902446</v>
+        <v>-5.797978049599556</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.939058581127972</v>
       </c>
       <c r="E5">
-        <v>-6.909158268846373</v>
+        <v>-5.032703551236023</v>
       </c>
       <c r="F5">
-        <v>-5.401504821088341</v>
+        <v>-4.87783662842798</v>
       </c>
       <c r="G5">
-        <v>-5.900879736596722</v>
+        <v>-5.724636223722542</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.599606201335993</v>
       </c>
       <c r="E6">
-        <v>-9.112555224388501</v>
+        <v>-6.636652816960802</v>
       </c>
       <c r="F6">
-        <v>-5.041830179895004</v>
+        <v>-4.516159823222076</v>
       </c>
       <c r="G6">
-        <v>-5.785858142380284</v>
+        <v>-5.514618525256717</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.245142298610705</v>
       </c>
       <c r="E7">
-        <v>-8.602875474825202</v>
+        <v>-7.92834568596068</v>
       </c>
       <c r="F7">
-        <v>-5.390383160338354</v>
+        <v>-4.729934942127739</v>
       </c>
       <c r="G7">
-        <v>-5.27853359121467</v>
+        <v>-5.671154360535616</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.829347269819136</v>
       </c>
       <c r="E8">
-        <v>-10.69424704036558</v>
+        <v>-9.303770039362382</v>
       </c>
       <c r="F8">
-        <v>-5.296684038305494</v>
+        <v>-4.497581199112089</v>
       </c>
       <c r="G8">
-        <v>-5.162429448606891</v>
+        <v>-5.23670153778044</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.30199112765226</v>
       </c>
       <c r="E9">
-        <v>-10.6479705644812</v>
+        <v>-8.810202600318375</v>
       </c>
       <c r="F9">
-        <v>-5.251471745460697</v>
+        <v>-4.258731398923685</v>
       </c>
       <c r="G9">
-        <v>-4.94158295568211</v>
+        <v>-5.281377349832905</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.63080800714165</v>
       </c>
       <c r="E10">
-        <v>-12.15054993954428</v>
+        <v>-10.12509031318554</v>
       </c>
       <c r="F10">
-        <v>-4.957396347262455</v>
+        <v>-4.548733714602362</v>
       </c>
       <c r="G10">
-        <v>-5.644342252213058</v>
+        <v>-4.562210989609328</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.79694409004817</v>
       </c>
       <c r="E11">
-        <v>-12.31175908574333</v>
+        <v>-11.05927827317587</v>
       </c>
       <c r="F11">
-        <v>-4.807194284684641</v>
+        <v>-4.150076931800682</v>
       </c>
       <c r="G11">
-        <v>-4.463960619094838</v>
+        <v>-4.477600066716636</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.79561612192981</v>
       </c>
       <c r="E12">
-        <v>-13.5765256482936</v>
+        <v>-11.90829469402994</v>
       </c>
       <c r="F12">
-        <v>-4.662059345509751</v>
+        <v>-4.582676068932071</v>
       </c>
       <c r="G12">
-        <v>-4.693901180615997</v>
+        <v>-4.248500383762451</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.63696234940574</v>
       </c>
       <c r="E13">
-        <v>-13.93225086701813</v>
+        <v>-13.00748666143776</v>
       </c>
       <c r="F13">
-        <v>-4.696786992137314</v>
+        <v>-4.098540882202914</v>
       </c>
       <c r="G13">
-        <v>-3.539321939430856</v>
+        <v>-3.502505362488622</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.34523241271727</v>
       </c>
       <c r="E14">
-        <v>-14.57508133782896</v>
+        <v>-13.48410402227106</v>
       </c>
       <c r="F14">
-        <v>-4.605366708829555</v>
+        <v>-4.059507381815599</v>
       </c>
       <c r="G14">
-        <v>-3.443107554423018</v>
+        <v>-2.565581248328404</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.949242997035334</v>
       </c>
       <c r="E15">
-        <v>-15.88026000242368</v>
+        <v>-15.57481895908032</v>
       </c>
       <c r="F15">
-        <v>-4.688789104863285</v>
+        <v>-4.051078743492114</v>
       </c>
       <c r="G15">
-        <v>-3.361784003250821</v>
+        <v>-2.599024379366122</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.486770395963596</v>
       </c>
       <c r="E16">
-        <v>-16.87618464856059</v>
+        <v>-16.37567053038881</v>
       </c>
       <c r="F16">
-        <v>-4.239649127432796</v>
+        <v>-3.663961946978834</v>
       </c>
       <c r="G16">
-        <v>-2.614590564491775</v>
+        <v>-1.596912312992116</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.001153885287398</v>
       </c>
       <c r="E17">
-        <v>-18.37839721722904</v>
+        <v>-16.57071643437318</v>
       </c>
       <c r="F17">
-        <v>-4.344314177143916</v>
+        <v>-3.552681555188957</v>
       </c>
       <c r="G17">
-        <v>-1.187172712687599</v>
+        <v>-1.467125685670528</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.53447547223074</v>
       </c>
       <c r="E18">
-        <v>-18.8891139873401</v>
+        <v>-17.90179344181777</v>
       </c>
       <c r="F18">
-        <v>-3.597440731064423</v>
+        <v>-3.421111132234909</v>
       </c>
       <c r="G18">
-        <v>-2.3019591964907</v>
+        <v>-1.03413612404371</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.125415869903472</v>
       </c>
       <c r="E19">
-        <v>-19.44575854083694</v>
+        <v>-19.47427434166325</v>
       </c>
       <c r="F19">
-        <v>-3.774674078730391</v>
+        <v>-3.072019712979739</v>
       </c>
       <c r="G19">
-        <v>-1.006354025878146</v>
+        <v>-0.5931482843940132</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.802040028761811</v>
       </c>
       <c r="E20">
-        <v>-19.6794685558988</v>
+        <v>-19.85094828114726</v>
       </c>
       <c r="F20">
-        <v>-3.640260698849935</v>
+        <v>-2.791990112463366</v>
       </c>
       <c r="G20">
-        <v>-1.450745106342214</v>
+        <v>-0.7023764239167267</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.5763454724251</v>
       </c>
       <c r="E21">
-        <v>-21.28694550287556</v>
+        <v>-21.11002255186989</v>
       </c>
       <c r="F21">
-        <v>-2.907206077783944</v>
+        <v>-2.626901459289841</v>
       </c>
       <c r="G21">
-        <v>-0.9920160531475629</v>
+        <v>-0.3641545388970859</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.449159593902181</v>
       </c>
       <c r="E22">
-        <v>-22.57727982967313</v>
+        <v>-21.42761801944983</v>
       </c>
       <c r="F22">
-        <v>-3.105383038494892</v>
+        <v>-2.504049603250257</v>
       </c>
       <c r="G22">
-        <v>-1.121094223723746</v>
+        <v>0.1537869318129698</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.403623586940273</v>
       </c>
       <c r="E23">
-        <v>-22.29237541595456</v>
+        <v>-21.76997971137773</v>
       </c>
       <c r="F23">
-        <v>-3.106649612253772</v>
+        <v>-2.372831236442399</v>
       </c>
       <c r="G23">
-        <v>-0.6558069798157989</v>
+        <v>-0.5112420772069047</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.412231893223023</v>
       </c>
       <c r="E24">
-        <v>-23.89298266786168</v>
+        <v>-23.3188446192732</v>
       </c>
       <c r="F24">
-        <v>-2.690787638495947</v>
+        <v>-1.973862159129865</v>
       </c>
       <c r="G24">
-        <v>-1.141093229326484</v>
+        <v>-0.1458869609473973</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.448001870448411</v>
       </c>
       <c r="E25">
-        <v>-22.26380527344017</v>
+        <v>-23.23265870195922</v>
       </c>
       <c r="F25">
-        <v>-2.923286345807087</v>
+        <v>-2.080485469381203</v>
       </c>
       <c r="G25">
-        <v>-1.944585805526376</v>
+        <v>-0.5963727557492634</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.479570759432989</v>
       </c>
       <c r="E26">
-        <v>-24.03436162638115</v>
+        <v>-23.70735598981327</v>
       </c>
       <c r="F26">
-        <v>-2.61016512428368</v>
+        <v>-1.634339211744432</v>
       </c>
       <c r="G26">
-        <v>-1.025293656908317</v>
+        <v>-0.5288707322035239</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.48117760884329</v>
       </c>
       <c r="E27">
-        <v>-25.10381963345461</v>
+        <v>-23.0786136016403</v>
       </c>
       <c r="F27">
-        <v>-2.467116014229039</v>
+        <v>-1.86912172798509</v>
       </c>
       <c r="G27">
-        <v>-2.224432841052048</v>
+        <v>-0.8766600938316584</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.436427989760041</v>
       </c>
       <c r="E28">
-        <v>-23.6012855431316</v>
+        <v>-22.99041704186691</v>
       </c>
       <c r="F28">
-        <v>-2.717493375194801</v>
+        <v>-1.882504003377316</v>
       </c>
       <c r="G28">
-        <v>-2.243220186987412</v>
+        <v>-0.9982200154881571</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.333453961307359</v>
       </c>
       <c r="E29">
-        <v>-23.58253766073985</v>
+        <v>-23.39920691901332</v>
       </c>
       <c r="F29">
-        <v>-2.620316766804988</v>
+        <v>-1.900177221916043</v>
       </c>
       <c r="G29">
-        <v>-2.359913606701182</v>
+        <v>-1.292083900827103</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.170400526830941</v>
       </c>
       <c r="E30">
-        <v>-22.30850131189588</v>
+        <v>-23.46807595172197</v>
       </c>
       <c r="F30">
-        <v>-2.669559067064405</v>
+        <v>-1.766515999637329</v>
       </c>
       <c r="G30">
-        <v>-1.480089782002314</v>
+        <v>-1.355619890816796</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.951423673347418</v>
       </c>
       <c r="E31">
-        <v>-22.77873805285237</v>
+        <v>-22.85872448924985</v>
       </c>
       <c r="F31">
-        <v>-2.812874083055344</v>
+        <v>-2.163067900868494</v>
       </c>
       <c r="G31">
-        <v>-2.651794475262105</v>
+        <v>-1.403775086231035</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.683989035709734</v>
       </c>
       <c r="E32">
-        <v>-22.78323029906798</v>
+        <v>-23.23084278388215</v>
       </c>
       <c r="F32">
-        <v>-2.71981611739225</v>
+        <v>-2.063492340480174</v>
       </c>
       <c r="G32">
-        <v>-2.389562852550895</v>
+        <v>-1.525639578077146</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.384677705866348</v>
       </c>
       <c r="E33">
-        <v>-21.51075174528264</v>
+        <v>-22.81976602736186</v>
       </c>
       <c r="F33">
-        <v>-2.364712407527561</v>
+        <v>-1.924990967466903</v>
       </c>
       <c r="G33">
-        <v>-2.262043948923708</v>
+        <v>-1.85108606786074</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.069905245049813</v>
       </c>
       <c r="E34">
-        <v>-22.24414716777287</v>
+        <v>-22.13507434282413</v>
       </c>
       <c r="F34">
-        <v>-2.440453352635131</v>
+        <v>-2.082778390352152</v>
       </c>
       <c r="G34">
-        <v>-2.566627380718814</v>
+        <v>-1.27406460145685</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.758572556701469</v>
       </c>
       <c r="E35">
-        <v>-21.48419224522766</v>
+        <v>-21.86886346980922</v>
       </c>
       <c r="F35">
-        <v>-2.997233875487597</v>
+        <v>-2.129425415538598</v>
       </c>
       <c r="G35">
-        <v>-2.286886282650399</v>
+        <v>-1.506560904134326</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.471880340180983</v>
       </c>
       <c r="E36">
-        <v>-20.36048311954231</v>
+        <v>-21.10015953548118</v>
       </c>
       <c r="F36">
-        <v>-2.696504201942667</v>
+        <v>-1.875009763484189</v>
       </c>
       <c r="G36">
-        <v>-2.726682325905958</v>
+        <v>-0.8818874452381676</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.225644583361576</v>
       </c>
       <c r="E37">
-        <v>-20.47876233214865</v>
+        <v>-20.70092021001695</v>
       </c>
       <c r="F37">
-        <v>-2.418542206463682</v>
+        <v>-1.955763988113501</v>
       </c>
       <c r="G37">
-        <v>-2.688905690757335</v>
+        <v>-1.51190743518025</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.035615992369274</v>
       </c>
       <c r="E38">
-        <v>-19.89727457024573</v>
+        <v>-20.17152348462425</v>
       </c>
       <c r="F38">
-        <v>-2.54499663233804</v>
+        <v>-2.076175473784438</v>
       </c>
       <c r="G38">
-        <v>-1.765928904954067</v>
+        <v>-1.011372812915682</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.914728479783558</v>
       </c>
       <c r="E39">
-        <v>-20.49594336253375</v>
+        <v>-19.98301669710696</v>
       </c>
       <c r="F39">
-        <v>-2.429354057805021</v>
+        <v>-2.295228121413336</v>
       </c>
       <c r="G39">
-        <v>-1.684092219223283</v>
+        <v>-0.5571394805633605</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.869799683174789</v>
       </c>
       <c r="E40">
-        <v>-19.56689069206812</v>
+        <v>-19.48595327612903</v>
       </c>
       <c r="F40">
-        <v>-2.848145138699144</v>
+        <v>-2.317867402531846</v>
       </c>
       <c r="G40">
-        <v>-1.349647666663951</v>
+        <v>-0.6691749627033761</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.904656338643512</v>
       </c>
       <c r="E41">
-        <v>-18.89151407856416</v>
+        <v>-17.99050171915402</v>
       </c>
       <c r="F41">
-        <v>-2.543649706941088</v>
+        <v>-2.232429588607105</v>
       </c>
       <c r="G41">
-        <v>-1.144678550145514</v>
+        <v>-0.02891876595386773</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.014909537691858</v>
       </c>
       <c r="E42">
-        <v>-18.29621899941185</v>
+        <v>-17.29658553306266</v>
       </c>
       <c r="F42">
-        <v>-2.231467854052455</v>
+        <v>-2.320625865983169</v>
       </c>
       <c r="G42">
-        <v>-1.243885668320854</v>
+        <v>-0.4684963132038352</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.191371955571852</v>
       </c>
       <c r="E43">
-        <v>-17.79997976070332</v>
+        <v>-17.64781850557158</v>
       </c>
       <c r="F43">
-        <v>-2.793337866227721</v>
+        <v>-2.1428300568507</v>
       </c>
       <c r="G43">
-        <v>-1.524888084239732</v>
+        <v>-0.3609962784526212</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.42151457222404</v>
       </c>
       <c r="E44">
-        <v>-17.20665456774434</v>
+        <v>-16.09889925598801</v>
       </c>
       <c r="F44">
-        <v>-2.944586985202674</v>
+        <v>-2.157457368449333</v>
       </c>
       <c r="G44">
-        <v>-1.053545852540457</v>
+        <v>0.04668747307200764</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.684374419946028</v>
       </c>
       <c r="E45">
-        <v>-16.44152812788236</v>
+        <v>-15.88328502306081</v>
       </c>
       <c r="F45">
-        <v>-2.743433700413467</v>
+        <v>-2.427597090543683</v>
       </c>
       <c r="G45">
-        <v>-0.824015798666168</v>
+        <v>-0.02595913824175929</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.961617068322551</v>
       </c>
       <c r="E46">
-        <v>-16.87281546389888</v>
+        <v>-15.26351354189703</v>
       </c>
       <c r="F46">
-        <v>-2.740986703105598</v>
+        <v>-2.161774819352724</v>
       </c>
       <c r="G46">
-        <v>-0.9677166488893124</v>
+        <v>0.6814680274995614</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.235264072143618</v>
       </c>
       <c r="E47">
-        <v>-15.20513698346415</v>
+        <v>-14.55407374690738</v>
       </c>
       <c r="F47">
-        <v>-2.928075137762671</v>
+        <v>-2.349284064650421</v>
       </c>
       <c r="G47">
-        <v>-1.022939859029895</v>
+        <v>0.342031172267008</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.490043307521607</v>
       </c>
       <c r="E48">
-        <v>-15.24359278473729</v>
+        <v>-14.03149690337023</v>
       </c>
       <c r="F48">
-        <v>-3.052950695367294</v>
+        <v>-2.413335088969684</v>
       </c>
       <c r="G48">
-        <v>-1.251248321600193</v>
+        <v>0.2081030524757922</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.717873293594644</v>
       </c>
       <c r="E49">
-        <v>-13.93293466659329</v>
+        <v>-13.60999107121029</v>
       </c>
       <c r="F49">
-        <v>-3.082906945754733</v>
+        <v>-2.235968374151865</v>
       </c>
       <c r="G49">
-        <v>-1.588384347682953</v>
+        <v>0.04243011150850489</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.912936678959339</v>
       </c>
       <c r="E50">
-        <v>-13.56600147469978</v>
+        <v>-12.79234338980735</v>
       </c>
       <c r="F50">
-        <v>-2.919533013105003</v>
+        <v>-2.651195818479145</v>
       </c>
       <c r="G50">
-        <v>-1.32362346817974</v>
+        <v>0.08347425510438906</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.078004994046173</v>
       </c>
       <c r="E51">
-        <v>-13.37420248657891</v>
+        <v>-11.92345602500762</v>
       </c>
       <c r="F51">
-        <v>-2.825718748003153</v>
+        <v>-2.46247964187557</v>
       </c>
       <c r="G51">
-        <v>-1.784275948332708</v>
+        <v>0.2012204282996474</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.221933441200972</v>
       </c>
       <c r="E52">
-        <v>-12.72091124081036</v>
+        <v>-11.78489377732092</v>
       </c>
       <c r="F52">
-        <v>-3.21820833549099</v>
+        <v>-2.543595863059906</v>
       </c>
       <c r="G52">
-        <v>-2.835867428336661</v>
+        <v>0.03283946108123626</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.351190400971175</v>
       </c>
       <c r="E53">
-        <v>-12.93257664440288</v>
+        <v>-11.28971873000419</v>
       </c>
       <c r="F53">
-        <v>-3.322436007213432</v>
+        <v>-2.571582255763488</v>
       </c>
       <c r="G53">
-        <v>-0.7499820687714465</v>
+        <v>-0.05503565971317813</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.477807759557909</v>
       </c>
       <c r="E54">
-        <v>-12.02831284065523</v>
+        <v>-10.07774511743535</v>
       </c>
       <c r="F54">
-        <v>-3.157209845051043</v>
+        <v>-2.729324946808986</v>
       </c>
       <c r="G54">
-        <v>-1.672482136017059</v>
+        <v>-0.1670810734898115</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.61156958005421</v>
       </c>
       <c r="E55">
-        <v>-11.51015125927557</v>
+        <v>-9.2270305188284</v>
       </c>
       <c r="F55">
-        <v>-2.904842745583756</v>
+        <v>-2.857259665232147</v>
       </c>
       <c r="G55">
-        <v>-1.802718997531987</v>
+        <v>-0.1384051280286444</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.758409098201504</v>
       </c>
       <c r="E56">
-        <v>-11.46783266967388</v>
+        <v>-8.841027922888587</v>
       </c>
       <c r="F56">
-        <v>-2.978298225027002</v>
+        <v>-2.734014334676234</v>
       </c>
       <c r="G56">
-        <v>-1.606042797589426</v>
+        <v>-0.3553253139438497</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.926113179185946</v>
       </c>
       <c r="E57">
-        <v>-9.843559612602681</v>
+        <v>-9.38053673074041</v>
       </c>
       <c r="F57">
-        <v>-3.36822567213798</v>
+        <v>-2.835379168654601</v>
       </c>
       <c r="G57">
-        <v>-1.910394491196783</v>
+        <v>-0.2033480998725273</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.115592994489596</v>
       </c>
       <c r="E58">
-        <v>-10.30967091373818</v>
+        <v>-8.041996798131184</v>
       </c>
       <c r="F58">
-        <v>-3.343671205584197</v>
+        <v>-2.783264090242276</v>
       </c>
       <c r="G58">
-        <v>-2.416977480161599</v>
+        <v>-0.4168286289724298</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.326545265178138</v>
       </c>
       <c r="E59">
-        <v>-8.737479836229197</v>
+        <v>-7.539286370065689</v>
       </c>
       <c r="F59">
-        <v>-3.5149080016213</v>
+        <v>-3.114962279140865</v>
       </c>
       <c r="G59">
-        <v>-2.207784107535053</v>
+        <v>-0.583110710318943</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.559915146196927</v>
       </c>
       <c r="E60">
-        <v>-8.676195997483394</v>
+        <v>-6.967625396759406</v>
       </c>
       <c r="F60">
-        <v>-3.432521064841069</v>
+        <v>-2.795701198427908</v>
       </c>
       <c r="G60">
-        <v>-2.34138779386342</v>
+        <v>-0.5400040968520928</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.812193835541921</v>
       </c>
       <c r="E61">
-        <v>-8.055971668918854</v>
+        <v>-6.716290560859693</v>
       </c>
       <c r="F61">
-        <v>-3.609297153700692</v>
+        <v>-2.936825182638442</v>
       </c>
       <c r="G61">
-        <v>-2.712963425191218</v>
+        <v>-0.9641743651622923</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.084645198987001</v>
       </c>
       <c r="E62">
-        <v>-8.274696963489331</v>
+        <v>-6.29974793621215</v>
       </c>
       <c r="F62">
-        <v>-3.53330107143306</v>
+        <v>-2.73994875874989</v>
       </c>
       <c r="G62">
-        <v>-2.319763310400901</v>
+        <v>-0.695761953929263</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.378405678837959</v>
       </c>
       <c r="E63">
-        <v>-8.198378591038063</v>
+        <v>-5.097347517695518</v>
       </c>
       <c r="F63">
-        <v>-3.438198695019858</v>
+        <v>-2.816915687613603</v>
       </c>
       <c r="G63">
-        <v>-3.052039430959991</v>
+        <v>-1.940609840333711</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.686205716086347</v>
       </c>
       <c r="E64">
-        <v>-7.585694171696295</v>
+        <v>-6.089400318555863</v>
       </c>
       <c r="F64">
-        <v>-3.48497494552114</v>
+        <v>-3.169415838731293</v>
       </c>
       <c r="G64">
-        <v>-1.970934437473435</v>
+        <v>-1.270972551923171</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.00656594312678</v>
       </c>
       <c r="E65">
-        <v>-7.212253562653759</v>
+        <v>-6.189674318507707</v>
       </c>
       <c r="F65">
-        <v>-3.432652775258115</v>
+        <v>-3.122925374983977</v>
       </c>
       <c r="G65">
-        <v>-3.231275677001672</v>
+        <v>-1.817781979735672</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.33358000621658</v>
       </c>
       <c r="E66">
-        <v>-6.491202760308438</v>
+        <v>-5.407670256019144</v>
       </c>
       <c r="F66">
-        <v>-3.456425262983655</v>
+        <v>-2.639928365066266</v>
       </c>
       <c r="G66">
-        <v>-3.450466897156818</v>
+        <v>-1.953957959948053</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.65669286838971</v>
       </c>
       <c r="E67">
-        <v>-6.441711067878609</v>
+        <v>-4.479967070807795</v>
       </c>
       <c r="F67">
-        <v>-3.59849027256377</v>
+        <v>-3.192220793330364</v>
       </c>
       <c r="G67">
-        <v>-3.27084993837812</v>
+        <v>-1.583147064639826</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.96690122738756</v>
       </c>
       <c r="E68">
-        <v>-7.386038281172116</v>
+        <v>-4.82734178346218</v>
       </c>
       <c r="F68">
-        <v>-3.379411945545385</v>
+        <v>-2.804544848820195</v>
       </c>
       <c r="G68">
-        <v>-3.924027194367404</v>
+        <v>-2.390794375491503</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.25127434153903</v>
       </c>
       <c r="E69">
-        <v>-6.391037443732777</v>
+        <v>-4.470366705911533</v>
       </c>
       <c r="F69">
-        <v>-3.581346380795432</v>
+        <v>-2.876344421825245</v>
       </c>
       <c r="G69">
-        <v>-3.504359267990613</v>
+        <v>-2.099794112044027</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.49970330356504</v>
       </c>
       <c r="E70">
-        <v>-7.262977000013674</v>
+        <v>-4.709266352186183</v>
       </c>
       <c r="F70">
-        <v>-4.095212501978466</v>
+        <v>-2.987555230753287</v>
       </c>
       <c r="G70">
-        <v>-4.072243628706114</v>
+        <v>-2.181673834866821</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.70624049612163</v>
       </c>
       <c r="E71">
-        <v>-5.719369650441102</v>
+        <v>-4.162267448325673</v>
       </c>
       <c r="F71">
-        <v>-3.624707272494972</v>
+        <v>-3.196351861568125</v>
       </c>
       <c r="G71">
-        <v>-3.80058357229906</v>
+        <v>-2.550316322846825</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.86343391290529</v>
       </c>
       <c r="E72">
-        <v>-6.609635941031041</v>
+        <v>-4.163485607833736</v>
       </c>
       <c r="F72">
-        <v>-3.906272666176135</v>
+        <v>-3.029207200500852</v>
       </c>
       <c r="G72">
-        <v>-3.841319835159792</v>
+        <v>-2.173566308841146</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.96933915662235</v>
       </c>
       <c r="E73">
-        <v>-7.347704748697186</v>
+        <v>-4.913486944510093</v>
       </c>
       <c r="F73">
-        <v>-3.709808769254176</v>
+        <v>-3.207233295771299</v>
       </c>
       <c r="G73">
-        <v>-3.370391421652926</v>
+        <v>-2.113188579295918</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.02619228607785</v>
       </c>
       <c r="E74">
-        <v>-7.458765573735302</v>
+        <v>-4.512789450415389</v>
       </c>
       <c r="F74">
-        <v>-3.696634414080053</v>
+        <v>-3.255258724316003</v>
       </c>
       <c r="G74">
-        <v>-3.447156351617546</v>
+        <v>-1.839922908302317</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.03263284844004</v>
       </c>
       <c r="E75">
-        <v>-7.097755625843821</v>
+        <v>-4.563408732873128</v>
       </c>
       <c r="F75">
-        <v>-3.738821509169826</v>
+        <v>-3.392139810689399</v>
       </c>
       <c r="G75">
-        <v>-3.584994225690642</v>
+        <v>-1.4686154311632</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.99407767173994</v>
       </c>
       <c r="E76">
-        <v>-8.351119490842777</v>
+        <v>-5.188614382846106</v>
       </c>
       <c r="F76">
-        <v>-3.95455571698311</v>
+        <v>-3.717736245298967</v>
       </c>
       <c r="G76">
-        <v>-2.347009100189103</v>
+        <v>-1.072055112650522</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.91746732921217</v>
       </c>
       <c r="E77">
-        <v>-7.045392880893129</v>
+        <v>-6.183284641682884</v>
       </c>
       <c r="F77">
-        <v>-3.755709435410699</v>
+        <v>-3.672634953686146</v>
       </c>
       <c r="G77">
-        <v>-1.825114838105157</v>
+        <v>-1.164571618290995</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.80907136661724</v>
       </c>
       <c r="E78">
-        <v>-8.081466977582037</v>
+        <v>-6.577990964665441</v>
       </c>
       <c r="F78">
-        <v>-3.994302441704236</v>
+        <v>-3.587567419990456</v>
       </c>
       <c r="G78">
-        <v>-2.095526818843906</v>
+        <v>-1.15587150461379</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.67989284323856</v>
       </c>
       <c r="E79">
-        <v>-10.25211400910069</v>
+        <v>-6.980540604629281</v>
       </c>
       <c r="F79">
-        <v>-4.078206119198992</v>
+        <v>-3.437111876987384</v>
       </c>
       <c r="G79">
-        <v>-1.970543793099801</v>
+        <v>-0.213733281229221</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.54008578854315</v>
       </c>
       <c r="E80">
-        <v>-9.652326683732769</v>
+        <v>-7.334884638781472</v>
       </c>
       <c r="F80">
-        <v>-4.264397431958834</v>
+        <v>-3.975045384691355</v>
       </c>
       <c r="G80">
-        <v>-2.31108968108801</v>
+        <v>-0.8253234641541801</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.39856849609166</v>
       </c>
       <c r="E81">
-        <v>-9.172358252133796</v>
+        <v>-7.935650114535052</v>
       </c>
       <c r="F81">
-        <v>-4.511350322081422</v>
+        <v>-3.880188205029381</v>
       </c>
       <c r="G81">
-        <v>-2.094460823180261</v>
+        <v>-0.1073257265059665</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.26678696346788</v>
       </c>
       <c r="E82">
-        <v>-10.6169776883727</v>
+        <v>-8.695315214743777</v>
       </c>
       <c r="F82">
-        <v>-4.550647243302828</v>
+        <v>-3.730418550235828</v>
       </c>
       <c r="G82">
-        <v>-2.399388551711451</v>
+        <v>0.2885824145354747</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.14953187008454</v>
       </c>
       <c r="E83">
-        <v>-11.51707529603329</v>
+        <v>-10.37571417866605</v>
       </c>
       <c r="F83">
-        <v>-4.477030232216036</v>
+        <v>-4.207916857333755</v>
       </c>
       <c r="G83">
-        <v>-1.900433059669116</v>
+        <v>0.2131052867856309</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.04850897173593</v>
       </c>
       <c r="E84">
-        <v>-12.36811141629478</v>
+        <v>-10.95511884252545</v>
       </c>
       <c r="F84">
-        <v>-4.491708902593643</v>
+        <v>-4.244740273490401</v>
       </c>
       <c r="G84">
-        <v>-1.553825562798501</v>
+        <v>0.1493938378823569</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.96617517946097</v>
       </c>
       <c r="E85">
-        <v>-13.44913061750982</v>
+        <v>-11.75443073267133</v>
       </c>
       <c r="F85">
-        <v>-4.912407713616414</v>
+        <v>-4.345044797193185</v>
       </c>
       <c r="G85">
-        <v>-1.088210574882166</v>
+        <v>0.1518668154001925</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.89615808985576</v>
       </c>
       <c r="E86">
-        <v>-14.22274341766217</v>
+        <v>-13.58488521131176</v>
       </c>
       <c r="F86">
-        <v>-4.403991421576398</v>
+        <v>-4.487655700891746</v>
       </c>
       <c r="G86">
-        <v>-1.150915617941501</v>
+        <v>0.8519114645889385</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.83479020340197</v>
       </c>
       <c r="E87">
-        <v>-15.98458698661239</v>
+        <v>-14.15315888606031</v>
       </c>
       <c r="F87">
-        <v>-4.6748567935156</v>
+        <v>-4.496044577579896</v>
       </c>
       <c r="G87">
-        <v>-0.7037867163164563</v>
+        <v>0.7872399574792758</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.78048407793137</v>
       </c>
       <c r="E88">
-        <v>-17.17881350954518</v>
+        <v>-16.21989102452495</v>
       </c>
       <c r="F88">
-        <v>-5.19426966282778</v>
+        <v>-4.559371608789113</v>
       </c>
       <c r="G88">
-        <v>-1.108577051039762</v>
+        <v>1.109091194807221</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.73063008846715</v>
       </c>
       <c r="E89">
-        <v>-19.16843479260721</v>
+        <v>-17.45580667917235</v>
       </c>
       <c r="F89">
-        <v>-4.983262947782273</v>
+        <v>-4.78704341924414</v>
       </c>
       <c r="G89">
-        <v>-1.170120092614813</v>
+        <v>0.8568044508959812</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.68782206080833</v>
       </c>
       <c r="E90">
-        <v>-20.51910650708299</v>
+        <v>-18.7405166412524</v>
       </c>
       <c r="F90">
-        <v>-5.139933731408549</v>
+        <v>-4.747496331067088</v>
       </c>
       <c r="G90">
-        <v>-1.39607475730669</v>
+        <v>1.349767855512236</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.65314076771429</v>
       </c>
       <c r="E91">
-        <v>-23.40042507852138</v>
+        <v>-20.75464149716994</v>
       </c>
       <c r="F91">
-        <v>-4.833209991336962</v>
+        <v>-4.66035456539479</v>
       </c>
       <c r="G91">
-        <v>-1.212726813705234</v>
+        <v>0.6186404942552728</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.62555632722727</v>
       </c>
       <c r="E92">
-        <v>-24.51519046804158</v>
+        <v>-23.25386554573714</v>
       </c>
       <c r="F92">
-        <v>-5.00143318676268</v>
+        <v>-4.884147959669909</v>
       </c>
       <c r="G92">
-        <v>-1.119336324042393</v>
+        <v>0.7329569422718462</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.60546544399283</v>
       </c>
       <c r="E93">
-        <v>-26.49011232447472</v>
+        <v>-25.49237176026073</v>
       </c>
       <c r="F93">
-        <v>-4.987471882555897</v>
+        <v>-4.835231207799793</v>
       </c>
       <c r="G93">
-        <v>-2.101310341901013</v>
+        <v>0.2370703259444151</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.58288553106305</v>
       </c>
       <c r="E94">
-        <v>-28.86944049521484</v>
+        <v>-27.66732989903469</v>
       </c>
       <c r="F94">
-        <v>-5.181432453186596</v>
+        <v>-4.945708911576357</v>
       </c>
       <c r="G94">
-        <v>-1.588877618968304</v>
+        <v>0.2091193899563484</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.54813635717098</v>
       </c>
       <c r="E95">
-        <v>-31.02613076984185</v>
+        <v>-29.526639814052</v>
       </c>
       <c r="F95">
-        <v>-5.145576570156419</v>
+        <v>-4.976674113460406</v>
       </c>
       <c r="G95">
-        <v>-1.959158826990248</v>
+        <v>0.378470347017766</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.4893511122661</v>
       </c>
       <c r="E96">
-        <v>-33.42257430809396</v>
+        <v>-32.06115878903499</v>
       </c>
       <c r="F96">
-        <v>-5.019549581861905</v>
+        <v>-4.910448624708794</v>
       </c>
       <c r="G96">
-        <v>-2.831795457323357</v>
+        <v>-0.6008817187737507</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.39750061842112</v>
       </c>
       <c r="E97">
-        <v>-35.47998911128782</v>
+        <v>-34.96656204948318</v>
       </c>
       <c r="F97">
-        <v>-5.466220196064649</v>
+        <v>-5.125187134903912</v>
       </c>
       <c r="G97">
-        <v>-2.49678480147681</v>
+        <v>-0.4909087065047011</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.25611390707533</v>
       </c>
       <c r="E98">
-        <v>-38.22696370857767</v>
+        <v>-37.50474908841237</v>
       </c>
       <c r="F98">
-        <v>-5.227232058519978</v>
+        <v>-5.092854298437842</v>
       </c>
       <c r="G98">
-        <v>-2.898032852473095</v>
+        <v>-1.605072807746419</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.07373467125672</v>
       </c>
       <c r="E99">
-        <v>-41.48977678008124</v>
+        <v>-40.21707633106953</v>
       </c>
       <c r="F99">
-        <v>-5.649233891467352</v>
+        <v>-5.576478382479472</v>
       </c>
       <c r="G99">
-        <v>-3.396693705962436</v>
+        <v>-1.383183492976768</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.831469343691612</v>
       </c>
       <c r="E100">
-        <v>-43.9895691521364</v>
+        <v>-42.84362295483639</v>
       </c>
       <c r="F100">
-        <v>-5.354343379744757</v>
+        <v>-5.251974564474196</v>
       </c>
       <c r="G100">
-        <v>-3.580614373942186</v>
+        <v>-2.294020508287528</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.57044457199107</v>
       </c>
       <c r="E101">
-        <v>-46.17017203376092</v>
+        <v>-45.59141947015863</v>
       </c>
       <c r="F101">
-        <v>-5.817698141807285</v>
+        <v>-5.576933984551012</v>
       </c>
       <c r="G101">
-        <v>-4.690699883079522</v>
+        <v>-2.998392040496102</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.251673654986103</v>
       </c>
       <c r="E102">
-        <v>-48.71917986133145</v>
+        <v>-47.81396054956818</v>
       </c>
       <c r="F102">
-        <v>-5.11410523578926</v>
+        <v>-5.276637547157746</v>
       </c>
       <c r="G102">
-        <v>-5.243845695054187</v>
+        <v>-3.317902722127782</v>
       </c>
     </row>
   </sheetData>
